--- a/social media/C1/Reading4.xlsx
+++ b/social media/C1/Reading4.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,313 +413,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI51"/>
+  <dimension ref="A1:AK51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>f2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>f3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>f4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>f5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>f6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>k1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k3</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>k4</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>k5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>k6</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>b1</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>b2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>b3</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>b4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>b5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>b6</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>a3</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>a4</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>a5</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>a6</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_1</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_2</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_3</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_4</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_5</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>r1p1_6</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_1</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_2</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_3</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_4</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_5</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>r1p2_6</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_1</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_2</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_3</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_4</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_5</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>r2p1_6</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_1</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_2</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_3</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_4</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_5</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>r2p2_6</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_1</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_2</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_3</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_4</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_5</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>r3p1_6</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_1</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_2</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_3</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_4</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_5</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>r3p2_6</t>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>s1</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>s2</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>s3</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>s4</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>s5</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>s6</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>r1_1</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>r1_2</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>r1_3</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>r1_4</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>r1_5</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>r1_6</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>r2_1</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>r2_2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>r2_3</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>r2_4</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>r2_5</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>r2_6</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>r3_1</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>r3_2</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>r3_3</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>r3_4</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>r3_5</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>r3_6</t>
         </is>
       </c>
     </row>
@@ -795,192 +671,97 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ surprised when you won the lottery.</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>There</t>
+          <t>There (1) _________ the company is about to go bankrupt.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>I would not have passed the exam</t>
+          <t>I would not have passed the exam (1) _________ help.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ the outdoor concert will be cancelled.</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ harder for the final test.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>The old factory is</t>
+          <t>The old factory is (1) _________ next month.</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>surprised when you won the lottery.</t>
+          <t>must have been (very/highly)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>the company is about to go bankrupt.</t>
+          <t>is a rumour (that)</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>help.</t>
+          <t>but for his</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>the outdoor concert will be cancelled.</t>
+          <t>every probability (that)</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>harder for the final test.</t>
+          <t>wish (that) I had studied</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>next month.</t>
+          <t>going to be pulled down</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>must</t>
+          <t>must have been quite</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>is a</t>
+          <t>is a widespread rumour (that)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>but</t>
+          <t>but for the help he gave</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>every</t>
+          <t>a high probability (that)</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>wish (that)</t>
+          <t>wish I'd studied</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>going to</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>have been (very/highly)</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>rumour (that)</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>for his</t>
+          <t>due to be pulled down</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>probability (that)</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>I had studied</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>be pulled down</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>is a</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>but</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>a high</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>due to</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>have been quite</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>widespread rumour (that)</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>for the help he gave</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>probability (that)</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>I'd studied</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>be pulled down</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>a strong</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>probability (that)</t>
+          <t>a strong probability (that)</t>
         </is>
       </c>
     </row>
@@ -1052,142 +833,72 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>His</t>
+          <t>His (1) _________ he was bringing a friend was unexpected.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>At no</t>
+          <t>At no (1) _________ found for this problem.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>The person you saw at the cinema yesterday</t>
+          <t>The person you saw at the cinema yesterday (1) _________ John.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ that I fell asleep.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>You can stay here</t>
+          <t>You can stay here (1) _________ keep quiet.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>The manager</t>
+          <t>The manager (1) _________ harder.</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>he was bringing a friend was unexpected.</t>
+          <t>failure to mention (that)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>found for this problem.</t>
+          <t>time has a solution been</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>John.</t>
+          <t>must have been</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>that I fell asleep.</t>
+          <t>was such a boring meeting</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>keep quiet.</t>
+          <t>on (the) condition (that) you</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>harder.</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>failure to</t>
+          <t>urged the staff to work</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>time has</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>on (the)</t>
+          <t>point has a solution been</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>urged the staff</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mention (that)</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>a solution been</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>such a boring meeting</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>condition (that) you</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>to work</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>point has</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>urged them</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>a solution been</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>to work</t>
+          <t>urged them to work</t>
         </is>
       </c>
     </row>
@@ -1259,128 +970,67 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>A new health campaign</t>
+          <t>A new health campaign (1) _________ by the government.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ the lecturer's accent.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ in the house.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ my car without asking.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>A new traffic management scheme</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
+          <t>A new traffic management scheme (1) _________ by the town council.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>(1) _________ you were coming, I would have cooked more food.</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>by the government.</t>
+          <t>has (recently) been set up</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>the lecturer's accent.</t>
+          <t>had (great/some) difficulty (in) understanding</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>in the house.</t>
+          <t>would ('d) rather you did not smoke</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>my car without asking.</t>
+          <t>ought not to have borrowed</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>by the town council.</t>
+          <t>is under consideration</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>you were coming, I would have cooked more food.</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>has (recently)</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>had (great/some)</t>
+          <t>Had I known (that)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>would ('d)</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ought</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>Had I</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>been set up</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>difficulty (in) understanding</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>rather you did not smoke</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>not to have borrowed</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>under consideration</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>known (that)</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>would ('d)</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>rather you didn't smoke</t>
+          <t>would ('d) rather you didn't smoke</t>
         </is>
       </c>
     </row>
@@ -1452,152 +1102,77 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>The heavy snowfall</t>
+          <t>The heavy snowfall (1) _________ off.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>I'm sure he</t>
+          <t>I'm sure he (1) _________ about the meeting.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>The text message</t>
+          <t>The text message (1) _________ by mistake.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>The price of the holiday</t>
+          <t>The price of the holiday (1) _________ the cost of the excursion.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ in cash if possible.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (1) _________ the conference began.</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>off.</t>
+          <t>prevented the plane (from) taking</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>about the meeting.</t>
+          <t>had no intention of forgetting</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>by mistake.</t>
+          <t>might have been sent</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>the cost of the excursion.</t>
+          <t>takes account of</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>in cash if possible.</t>
+          <t>would ('d) rather you paid</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>the conference began.</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>prevented the plane</t>
+          <t>sooner had he arrived than</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>had no</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>might have</t>
+          <t>had no intention of forgetting</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>takes</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>would ('d)</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>sooner had</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>(from) taking</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>intention of forgetting</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>been sent</t>
+          <t>takes into account</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>account of</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>rather you paid</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>he arrived than</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>takes</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>no intention of forgetting</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>into account</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>accounts</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>for</t>
+          <t>accounts for</t>
         </is>
       </c>
     </row>
@@ -1669,142 +1244,72 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>The company decided</t>
+          <t>The company decided (1) _________ until next month.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>It is</t>
+          <t>It is (1) _________ studying.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>I am</t>
+          <t>I am (1) _________ what he is saying.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>She was</t>
+          <t>She was (1) _________ that she couldn't speak.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>The bridge</t>
+          <t>The bridge (1) _________ twenty years ago.</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>There</t>
+          <t>There (1) _________ trying to fix that old car.</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>until next month.</t>
+          <t>to put off the launch</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>studying.</t>
+          <t>(high/about) time you started</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>what he is saying.</t>
+          <t>having (great) difficulty (in) understanding</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>that she couldn't speak.</t>
+          <t>in such a rage</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>twenty years ago.</t>
+          <t>was under construction</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>trying to fix that old car.</t>
+          <t>is no point (in)</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>to put</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>(high/about) time</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>having (great)</t>
+          <t>to put the launch off</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>was under</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>off the launch</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>you started</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>difficulty (in) understanding</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>such a rage</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>no point (in)</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>to put</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>the launch off</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>such an angry state</t>
+          <t>in such an angry state</t>
         </is>
       </c>
     </row>
@@ -1876,142 +1381,72 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>If it</t>
+          <t>If it (1) _________ his teacher's encouragement, James wouldn't have succeeded.</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>I am</t>
+          <t>I am (1) _________ them by email.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>The manager</t>
+          <t>The manager (1) _________ late.</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>There was</t>
+          <t>There was (1) _________ for the meeting.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>The hotel is going</t>
+          <t>The hotel is going (1) _________ during the summer.</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Under (1) _________ leave the building without permission.</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>his teacher's encouragement, James wouldn't have succeeded.</t>
+          <t>had not been for</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>them by email.</t>
+          <t>in favour of contacting</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>late.</t>
+          <t>apologised for being</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>for the meeting.</t>
+          <t>a very poor turnout</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>during the summer.</t>
+          <t>to be done up</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>leave the building without permission.</t>
+          <t>no circumstances should you</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>had not</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>apologised</t>
+          <t>hadn't been for</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>been for</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>favour of contacting</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>for being</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>very poor turnout</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>be done up</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>circumstances should you</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>hadn't</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>been for</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>low turnout</t>
+          <t>a low turnout</t>
         </is>
       </c>
     </row>
@@ -2083,132 +1518,67 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>There</t>
+          <t>There (1) _________ to convince her.</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>There</t>
+          <t>There (1) _________ the company's profits this year.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>He didn't mention the problem</t>
+          <t>He didn't mention the problem (1) _________ you.</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>The hotel was</t>
+          <t>The hotel was (1) _________ we had expected.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>The thief is</t>
+          <t>The thief is (1) _________ through the window.</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>You can use my car</t>
+          <t>You can use my car (1) _________ carefully.</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>to convince her.</t>
+          <t>is no point (in) trying</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>the company's profits this year.</t>
+          <t>has been a significant fall in</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>you.</t>
+          <t>for fear of worrying</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>we had expected.</t>
+          <t>not nearly as cheap as</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>through the window.</t>
+          <t>thought to have entered</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>carefully.</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>has</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>not</t>
+          <t>provided (that) you drive</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>thought</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>provided</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>no point (in) trying</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>been a significant fall in</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>fear of worrying</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>nearly as cheap as</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>to have entered</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>(that) you drive</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>believed</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>to have entered</t>
+          <t>believed to have entered</t>
         </is>
       </c>
     </row>
@@ -2280,152 +1650,77 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>I was</t>
+          <t>I was (1) _________ the office when the phone rang.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ the weather improving tomorrow.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>He was unable to</t>
+          <t>He was unable to (1) _________ his lateness for the meeting.</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ about the problem earlier.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>A quiet holiday</t>
+          <t>A quiet holiday (1) _________ want.</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>The match went ahead</t>
+          <t>The match went ahead (1) _________ raining.</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>the office when the phone rang.</t>
+          <t>on the point of leaving</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>the weather improving tomorrow.</t>
+          <t>little likelihood of</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>his lateness for the meeting.</t>
+          <t>account for</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>about the problem earlier.</t>
+          <t>wish (that) you had told me</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>want.</t>
+          <t>is all (that) I</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>raining.</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>on the</t>
+          <t>even though it was</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>little</t>
+          <t>little prospect of</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>give an account of</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>even</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>point of leaving</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>likelihood of</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>(that) you had told me</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>all (that) I</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>though it was</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>little</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>give</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>prospect of</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>an account of</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>(that) you'd told me</t>
+          <t>wish (that) you'd told me</t>
         </is>
       </c>
     </row>
@@ -2497,158 +1792,82 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>I was</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>I was (1) _________ that I fell asleep on the bus.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>(1) _________ , the government is planning to increase taxes.</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>There</t>
+          <t>There (1) _________ how much the repair will cost.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Losing his job</t>
+          <t>Losing his job (1) _________ to him.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ about the weather.</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>The bridge was closed</t>
+          <t>The bridge was closed (1) _________ its lack of safety.</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>that I fell asleep on the bus.</t>
+          <t>in such a tired state</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>, the government is planning to increase taxes.</t>
+          <t>According to the report</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>how much the repair will cost.</t>
+          <t>is no (way of) knowing</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>to him.</t>
+          <t>came as a (great) shock</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>about the weather.</t>
+          <t>never stops complaining</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>its lack of safety.</t>
+          <t>on account of</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>According</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>is</t>
+          <t>in such a state of tiredness</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>came as</t>
+          <t>came as a (great) blow</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>such a tired state</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>to the report</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>no (way of) knowing</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>a (great) shock</t>
+          <t>does not ever stop complaining</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>stops complaining</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>account of</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>came as</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>does not</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>such a state of tiredness</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>a (great) blow</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>ever stop complaining</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>doesn't</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>ever stop complaining</t>
+          <t>doesn't ever stop complaining</t>
         </is>
       </c>
     </row>
@@ -2720,172 +1939,87 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>The results of the competition</t>
+          <t>The results of the competition (1) _________ tomorrow.</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ that letter because it's not his handwriting.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>The match</t>
+          <t>The match (1) _________ the pitch was waterlogged.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>If</t>
+          <t>If (1) _________ your advice earlier.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ me with my luggage.</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>He is</t>
+          <t>He is (1) _________ that he can solve any problem.</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>tomorrow.</t>
+          <t>are likely to be announced</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>that letter because it's not his handwriting.</t>
+          <t>can't have written</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>the pitch was waterlogged.</t>
+          <t>was put off because</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>your advice earlier.</t>
+          <t>only I had taken</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>me with my luggage.</t>
+          <t>really appreciate your helping</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>that he can solve any problem.</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>are</t>
+          <t>such an intelligent person</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>was</t>
+          <t>cannot have written</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>only</t>
+          <t>only I'd taken</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>really</t>
+          <t>really appreciate you helping</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>likely to be announced</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>have written</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>put off because</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>I had taken</t>
+          <t>such an intelligent man</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>appreciate your helping</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>an intelligent person</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>cannot</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>only</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>really</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>have written</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>I'd taken</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>appreciate you helping</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>an intelligent man</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>do</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>appreciate your helping</t>
+          <t>do appreciate your helping</t>
         </is>
       </c>
     </row>
@@ -2957,152 +2091,77 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>The company's success can</t>
+          <t>The company's success can (1) _________ its innovative marketing strategy.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>If I had had enough money, I</t>
+          <t>If I had had enough money, I (1) _________ to buy the tickets.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>At no</t>
+          <t>At no (1) _________ that his friends were planning a surprise party.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>The bridge is</t>
+          <t>The bridge is (1) _________ built in the 17th century.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ at home tonight.</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Such</t>
+          <t>Such (1) _________ that he fell asleep in the meeting.</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>its innovative marketing strategy.</t>
+          <t>be put down to</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>to buy the tickets.</t>
+          <t>would have been able</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>that his friends were planning a surprise party.</t>
+          <t>time did he suspect</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>built in the 17th century.</t>
+          <t>said to have been</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>at home tonight.</t>
+          <t>would ('d) rather you stayed</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>that he fell asleep in the meeting.</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>be</t>
+          <t>was his exhaustion</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>would</t>
+          <t>might have been able</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>said</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>would ('d)</t>
+          <t>point did he suspect</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>put down to</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>have been able</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>did he suspect</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>to have been</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>rather you stayed</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>his exhaustion</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>point</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>have been able</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>did he suspect</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>his level of exhaustion</t>
+          <t>was his level of exhaustion</t>
         </is>
       </c>
     </row>
@@ -3174,132 +2233,67 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Under (1) _________ your bag be left unattended.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ that he won the race.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A lack of funding</t>
+          <t>A lack of funding (1) _________ the project.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (1) _________ the phone rang.</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>I was</t>
+          <t>I was (1) _________ you when you walked in.</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>A new shopping center is</t>
+          <t>A new shopping center is (1) _________ in the city.</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>your bag be left unattended.</t>
+          <t>no circumstances should</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>that he won the race.</t>
+          <t>find it hard to believe</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>the project.</t>
+          <t>resulted in the failure of</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>the phone rang.</t>
+          <t>sooner had he arrived than</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>you when you walked in.</t>
+          <t>on the point of calling</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>in the city.</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>find</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>resulted</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>sooner</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>on</t>
+          <t>under construction</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>circumstances should</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>it hard to believe</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>in the failure of</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>had he arrived than</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>the point of calling</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>construction</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>due</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>to be under construction</t>
+          <t>due to be under construction</t>
         </is>
       </c>
     </row>
@@ -3371,168 +2365,87 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>I wouldn't be late</t>
+          <t>I wouldn't be late (1) _________ a massive traffic jam.</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ Sarah yesterday because she's abroad.</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ tell him the news yet.</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>The manager said he would no</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
+          <t>The manager said he would no (1) _________ such rude behavior.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>(1) _________ any help, please don't hesitate to ask.</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ in a private jet before.</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>a massive traffic jam.</t>
+          <t>if it hadn't been for</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Sarah yesterday because she's abroad.</t>
+          <t>can't have seen</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>tell him the news yet.</t>
+          <t>had better not</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>such rude behavior.</t>
+          <t>longer put up with</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>any help, please don't hesitate to ask.</t>
+          <t>Should you (happen to) need</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>in a private jet before.</t>
+          <t>had never flown</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>if</t>
+          <t>if it were not for</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>can't</t>
+          <t>cannot have seen</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>longer</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>Should</t>
+          <t>'d better not</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>had</t>
+          <t>'d never flown</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>it hadn't been for</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>have seen</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>better not</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>put up with</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>you (happen to) need</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>never flown</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>if</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>cannot</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>'d</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>'d</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>it were not for</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>have seen</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>better not</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>never flown</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>if</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>there had not been</t>
+          <t>if there had not been</t>
         </is>
       </c>
     </row>
@@ -3604,142 +2517,72 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>They are going to</t>
+          <t>They are going to (1) _________ before winter starts.</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>His failure to pass the exam</t>
+          <t>His failure to pass the exam (1) _________ to me.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ with him.</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Not until he tried to sell it</t>
+          <t>Not until he tried to sell it (1) _________ how much the house was worth.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ our appointment.</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ check your spelling before you hand in the essay.</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>before winter starts.</t>
+          <t>have the roof repaired</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>to me.</t>
+          <t>came as a (great/total) surprise</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>with him.</t>
+          <t>is not worth arguing</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>how much the house was worth.</t>
+          <t>did he realize</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>our appointment.</t>
+          <t>can't have forgotten</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>check your spelling before you hand in the essay.</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>came as</t>
+          <t>is advisable (for you) to</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>did</t>
+          <t>isn't worth arguing</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>the roof repaired</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>a (great/total) surprise</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>not worth arguing</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>he realize</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>have forgotten</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>advisable (for you) to</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>isn't</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>cannot</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>worth arguing</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>have forgotten</t>
+          <t>cannot have forgotten</t>
         </is>
       </c>
     </row>
@@ -3811,132 +2654,67 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>She was</t>
+          <t>She was (1) _________ her eyes open.</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Would</t>
+          <t>Would (1) _________ in the office?</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>The CEO</t>
+          <t>The CEO (1) _________ resigning.</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>The car cost</t>
+          <t>The car cost (1) _________ I couldn't afford it.</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>It was only by</t>
+          <t>It was only by (1) _________ that he passed the test.</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>I was</t>
+          <t>I was (1) _________ leaving when the phone rang.</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>her eyes open.</t>
+          <t>far too exhausted to keep</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>in the office?</t>
+          <t>you mind not smoking</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>resigning.</t>
+          <t>is rumored to be</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>I couldn't afford it.</t>
+          <t>so much (money) that</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>that he passed the test.</t>
+          <t>working very hard</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>leaving when the phone rang.</t>
+          <t>on the verge of</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>far</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>you</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>so</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>working</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>too exhausted to keep</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>mind not smoking</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>rumored to be</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>much (money) that</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>very hard</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>the verge of</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>much</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>too exhausted to keep</t>
+          <t>much too exhausted to keep</t>
         </is>
       </c>
     </row>
@@ -4008,162 +2786,82 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>The criminal is</t>
+          <t>The criminal is (1) _________ through the back window.</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Thomas (1) _________ late.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>If my parents</t>
+          <t>If my parents (1) _________ the money, I wouldn't have been able to buy the house.</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>The flooding</t>
+          <t>The flooding (1) _________ by the heavy rain.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (1) _________ onto the court than it started to rain.</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ to convince him to change his mind.</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>through the back window.</t>
+          <t>thought to have escaped</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>late.</t>
+          <t>apologised for being</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>the money, I wouldn't have been able to buy the house.</t>
+          <t>had not lent me</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>by the heavy rain.</t>
+          <t>must have been caused</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>onto the court than it started to rain.</t>
+          <t>sooner had the players gone</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>to convince him to change his mind.</t>
+          <t>no point (in) trying</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>thought to</t>
+          <t>believed to have escaped</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>apologised</t>
+          <t>apologised for having been</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>had not</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>must</t>
+          <t>hadn't lent me</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>sooner</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>have escaped</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>for being</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>lent me</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>have been caused</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>had the players gone</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>point (in) trying</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>believed to</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>apologised</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>hadn't</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>sooner</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>have escaped</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>for having been</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>lent me</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>had the players stepped</t>
+          <t>sooner had the players stepped</t>
         </is>
       </c>
     </row>
@@ -4235,142 +2933,72 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (1) _________ at the moment.</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>The doctor</t>
+          <t>The doctor (1) _________ up a hobby.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ to the party.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Sarah (1) _________ her keys at the office.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Never (1) _________ such a beautiful sunrise.</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>The teacher said it</t>
+          <t>The teacher said it (1) _________ to finish the essay until Monday.</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>at the moment.</t>
+          <t>are having our living room decorated</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>up a hobby.</t>
+          <t>advised me to take</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>to the party.</t>
+          <t>wish I had gone</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>her keys at the office.</t>
+          <t>can't have forgotten</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>such a beautiful sunrise.</t>
+          <t>before have I seen</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>to finish the essay until Monday.</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>are</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>advised</t>
+          <t>was not necessary (for us)</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>before</t>
+          <t>wish I'd gone</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>having our living room decorated</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>me to take</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>I had gone</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>have forgotten</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>have I seen</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>not necessary (for us)</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>wasn't</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>I'd gone</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>necessary (for us)</t>
+          <t>wasn't necessary (for us)</t>
         </is>
       </c>
     </row>
@@ -4442,132 +3070,67 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ by the mechanic.</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>My mother</t>
+          <t>My mother (1) _________ the door.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>You will fail the exam</t>
+          <t>You will fail the exam (1) _________ harder.</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ exhausted after the long flight.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>It is</t>
+          <t>It is (1) _________ that I prefer to walk.</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ smoke in the house.</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>by the mechanic.</t>
+          <t>have just had my car repaired</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>the door.</t>
+          <t>reminded me to lock</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>harder.</t>
+          <t>unless you work</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>exhausted after the long flight.</t>
+          <t>must have been</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>that I prefer to walk.</t>
+          <t>such an unreliable bus service</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>smoke in the house.</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>reminded</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>unless</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>such</t>
+          <t>would prefer you not to</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>just had my car repaired</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>me to lock</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>you work</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>an unreliable bus service</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>prefer you not to</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>prefer it if you didn't</t>
+          <t>would prefer it if you didn't</t>
         </is>
       </c>
     </row>
@@ -4639,142 +3202,72 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>The old mansion</t>
+          <t>The old mansion (1) _________ haunted by a ghost.</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Sarah (1) _________ a call the following day.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>I wouldn't be late for the meeting</t>
+          <t>I wouldn't be late for the meeting (1) _________ the train.</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ to offend you with that comment.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (1) _________ his speech than the audience started cheering.</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Learning Chinese is</t>
+          <t>Learning Chinese is (1) _________ as I expected.</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>haunted by a ghost.</t>
+          <t>is said to be</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>a call the following day.</t>
+          <t>promised to give me</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>the train.</t>
+          <t>if I had not missed</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>to offend you with that comment.</t>
+          <t>can't have intended</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>his speech than the audience started cheering.</t>
+          <t>sooner had he finished</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>as I expected.</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>promised</t>
+          <t>not nearly as easy</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>if</t>
+          <t>had I not missed</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>sooner</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>said to be</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>to give me</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>I had not missed</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>have intended</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>had he finished</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>nearly as easy</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>I not missed</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>have meant</t>
+          <t>can't have meant</t>
         </is>
       </c>
     </row>
@@ -4846,142 +3339,72 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>I am</t>
+          <t>I am (1) _________ right now.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>The lifeguard</t>
+          <t>The lifeguard (1) _________ go near the water.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ your advice about the job.</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ about the meeting.</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Never (1) _________ such a spectacular sunset before I went to Africa.</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Driving a car</t>
+          <t>Driving a car (1) _________ riding a motorbike.</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>right now.</t>
+          <t>having my laptop repaired</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>go near the water.</t>
+          <t>warned the children not to</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>your advice about the job.</t>
+          <t>wish I had taken</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>about the meeting.</t>
+          <t>might have forgotten</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>such a spectacular sunset before I went to Africa.</t>
+          <t>before had I seen</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>riding a motorbike.</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>having</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>warned</t>
+          <t>is entirely different from</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>before</t>
+          <t>wish I'd taken</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>my laptop repaired</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>the children not to</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>I had taken</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>have forgotten</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>had I seen</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>entirely different from</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>I'd taken</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>very different from</t>
+          <t>is very different from</t>
         </is>
       </c>
     </row>
@@ -5053,152 +3476,77 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>The winner of the competition</t>
+          <t>The winner of the competition (1) _________ tomorrow.</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>The little boy</t>
+          <t>The little boy (1) _________ the vase.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>I wouldn't have been able to solve the puzzle</t>
+          <t>I wouldn't have been able to solve the puzzle (1) _________ hint.</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Mark (1) _________ at the party last night.</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ she started speaking that I realized who she was.</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>I am</t>
+          <t>I am (1) _________ up early in the morning.</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>tomorrow.</t>
+          <t>is going to be announced</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>the vase.</t>
+          <t>denied breaking</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>hint.</t>
+          <t>without your</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>at the party last night.</t>
+          <t>must have been</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>she started speaking that I realized who she was.</t>
+          <t>was only when</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>up early in the morning.</t>
+          <t>not used to getting</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>will be announced</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>denied having broken</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>without</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>going to be announced</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>breaking</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>your</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>only when</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>used to getting</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>without</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>be announced</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>having broken</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>the help of your</t>
+          <t>without the help of your</t>
         </is>
       </c>
     </row>
@@ -5270,142 +3618,72 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>The mountain</t>
+          <t>The mountain (1) _________ millions of years ago.</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Julia (1) _________ her birthday.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>If I had studied harder, I</t>
+          <t>If I had studied harder, I (1) _________ the exam.</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the one who stole the money.</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Hardly</t>
+          <t>Hardly (1) _________ when the lights went out.</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Travelling by train is</t>
+          <t>Travelling by train is (1) _________ travelling by bus.</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>millions of years ago.</t>
+          <t>is thought to have been formed</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>her birthday.</t>
+          <t>apologised for forgetting</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>the exam.</t>
+          <t>would have passed</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>the one who stole the money.</t>
+          <t>can't have been</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>when the lights went out.</t>
+          <t>had the match started</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>travelling by bus.</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>is</t>
+          <t>not as cheap as</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>apologised</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>had</t>
+          <t>apologised for having forgotten</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>thought to have been formed</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>for forgetting</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>have passed</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>the match started</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>as cheap as</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>apologised</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>for having forgotten</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>nearly as cheap as</t>
+          <t>not nearly as cheap as</t>
         </is>
       </c>
     </row>
@@ -5477,142 +3755,72 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>We are going</t>
+          <t>We are going (1) _________ next week.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>My friend</t>
+          <t>My friend (1) _________ a doctor.</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ to the concert with you.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ to send the email.</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Never before</t>
+          <t>Never before (1) _________ such a strange story.</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>The team</t>
+          <t>The team (1) _________ that they lost the game.</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>next week.</t>
+          <t>to have the house painted</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>a doctor.</t>
+          <t>advised me to see</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>to the concert with you.</t>
+          <t>wish I had gone</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>to send the email.</t>
+          <t>might have forgotten</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>such a strange story.</t>
+          <t>have I heard</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>that they lost the game.</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>to</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>advised</t>
+          <t>played in such a way</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>have</t>
+          <t>wish I'd gone</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>played</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>have the house painted</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>me to see</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>I had gone</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>have forgotten</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>I heard</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>in such a way</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>showed</t>
-        </is>
-      </c>
-      <c r="AT24" t="inlineStr">
-        <is>
-          <t>I'd gone</t>
-        </is>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>such a bad performance</t>
+          <t>showed such a bad performance</t>
         </is>
       </c>
     </row>
@@ -5684,142 +3892,72 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>The furniture</t>
+          <t>The furniture (1) _________ tomorrow afternoon.</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Mark (1) _________ for the coffee.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>You'll get wet</t>
+          <t>You'll get wet (1) _________ your umbrella.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ happy to see you.</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ I arrived at the office that I knew about the party.</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ his accent.</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>tomorrow afternoon.</t>
+          <t>will be delivered</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>for the coffee.</t>
+          <t>insisted on paying</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>your umbrella.</t>
+          <t>unless you take</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>happy to see you.</t>
+          <t>must have been very</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>I arrived at the office that I knew about the party.</t>
+          <t>was only when</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>his accent.</t>
+          <t>difficulty (in) understanding</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>insisted</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>unless</t>
+          <t>is going to be delivered</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>be delivered</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>on paying</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>you take</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>have been very</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>only when</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>(in) understanding</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>going to be delivered</t>
-        </is>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>have been quite</t>
+          <t>must have been quite</t>
         </is>
       </c>
     </row>
@@ -5891,142 +4029,72 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>The prisoner</t>
+          <t>The prisoner (1) _________ recaptured.</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Kevin (1) _________ her favorite mug.</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>If I</t>
+          <t>If I (1) _________ your birthday, I would have bought you a present.</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>The keys</t>
+          <t>The keys (1) _________ out of your pocket.</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Scarcely</t>
+          <t>Scarcely (1) _________ the match when it began to hail.</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ to get tickets for that show.</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>recaptured.</t>
+          <t>is reported to have been</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>her favorite mug.</t>
+          <t>apologised to his sister for breaking</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>your birthday, I would have bought you a present.</t>
+          <t>had known it was</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>out of your pocket.</t>
+          <t>must have fallen</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>the match when it began to hail.</t>
+          <t>had the team started</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>to get tickets for that show.</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>is</t>
+          <t>no point (in) trying</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>apologised</t>
+          <t>apologized to his sister for breaking</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>reported to have been</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>to his sister for breaking</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>known it was</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>have fallen</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>the team started</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>point (in) trying</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>apologized</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AS26" t="inlineStr">
-        <is>
-          <t>to his sister for breaking</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>known that it was</t>
+          <t>had known that it was</t>
         </is>
       </c>
     </row>
@@ -6098,162 +4166,82 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (1) _________ by a local decorator.</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>The nutritionist</t>
+          <t>The nutritionist (1) _________ too much sugar.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ my grandmother more often when I was younger.</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>The document</t>
+          <t>The document (1) _________ lost in the post.</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Not</t>
+          <t>Not (1) _________ to help with the housework.</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>The museum was</t>
+          <t>The museum was (1) _________ I had anticipated.</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>by a local decorator.</t>
+          <t>are having our house painted</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>too much sugar.</t>
+          <t>advised me to avoid eating</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>my grandmother more often when I was younger.</t>
+          <t>wish I had visited</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>lost in the post.</t>
+          <t>could have been</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>to help with the housework.</t>
+          <t>once did she offer</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>I had anticipated.</t>
+          <t>not nearly as boring as</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>are having the house exterior painted</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>advised</t>
+          <t>advised against eating</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>could</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>once</t>
+          <t>wish I'd visited</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>having our house painted</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr">
-        <is>
-          <t>me to avoid eating</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>I had visited</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>did she offer</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>nearly as boring as</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>are</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>advised</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>nothing</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>having the house exterior painted</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr">
-        <is>
-          <t>against eating</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr">
-        <is>
-          <t>I'd visited</t>
-        </is>
-      </c>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>like as dull as</t>
+          <t>nothing like as dull as</t>
         </is>
       </c>
     </row>
@@ -6325,142 +4313,72 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>A new library is</t>
+          <t>A new library is (1) _________ by the city council.</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ on Friday.</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>You won't be able to afford a holiday</t>
+          <t>You won't be able to afford a holiday (1) _________ saving now.</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>The flight</t>
+          <t>The flight (1) _________ due to the fog.</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Only when I reached the checkout</t>
+          <t>Only when I reached the checkout (1) _________ I’d forgotten my wallet.</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>The test</t>
+          <t>The test (1) _________ for me to complete in time.</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>by the city council.</t>
+          <t>going to be built</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>on Friday.</t>
+          <t>promised to pay me back</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>saving now.</t>
+          <t>unless you start</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>due to the fog.</t>
+          <t>must have been cancelled</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>I’d forgotten my wallet.</t>
+          <t>did I realize (that)</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>for me to complete in time.</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>going</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>promised</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>unless</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>must</t>
+          <t>was not easy enough</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>did</t>
+          <t>did I realise (that)</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>to be built</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>to pay me back</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>you start</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>have been cancelled</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>I realize (that)</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>not easy enough</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>wasn't</t>
-        </is>
-      </c>
-      <c r="AV28" t="inlineStr">
-        <is>
-          <t>I realise (that)</t>
-        </is>
-      </c>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>easy enough</t>
+          <t>wasn't easy enough</t>
         </is>
       </c>
     </row>
@@ -6532,152 +4450,77 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ the local council is reconsidering its decision.</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>My brother</t>
+          <t>My brother (1) _________ to the station.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Not</t>
+          <t>Not (1) _________ the truth, I wouldn't have been so angry.</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ it on purpose.</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>At no</t>
+          <t>At no (1) _________ been so happy.</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ the weather improving tomorrow.</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>the local council is reconsidering its decision.</t>
+          <t>is said that</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>to the station.</t>
+          <t>offered to take me</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>the truth, I wouldn't have been so angry.</t>
+          <t>having known</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>it on purpose.</t>
+          <t>can't have done</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>been so happy.</t>
+          <t>time had he ever</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>the weather improving tomorrow.</t>
+          <t>little chance of</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>is widely said that</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>offered</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>having</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>time</t>
+          <t>offered to drive me</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>little</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>said that</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>to take me</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>known</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>have done</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>had he ever</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>chance of</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>offered</t>
-        </is>
-      </c>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>very</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>widely said that</t>
-        </is>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>to drive me</t>
-        </is>
-      </c>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>little prospect of</t>
+          <t>very little prospect of</t>
         </is>
       </c>
     </row>
@@ -6749,152 +4592,77 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (1) _________ this afternoon.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Sam apologised</t>
+          <t>Sam apologised (1) _________ me with my homework.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ that house when I had the chance.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>The letter</t>
+          <t>The letter (1) _________ lost in the mail.</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Not until the following day</t>
+          <t>Not until the following day (1) _________ my mistake.</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>The car I saw yesterday was</t>
+          <t>The car I saw yesterday was (1) _________ this one.</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>this afternoon.</t>
+          <t>are having the grass cut</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>me with my homework.</t>
+          <t>for not helping</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>that house when I had the chance.</t>
+          <t>wish I had bought</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>lost in the mail.</t>
+          <t>may have been</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>my mistake.</t>
+          <t>did I realise</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>this one.</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>are</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>for</t>
+          <t>not nearly as expensive as</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>wish</t>
+          <t>wish I'd bought</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>may</t>
+          <t>may have got</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>having the grass cut</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>not helping</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>I had bought</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>I realise</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>nearly as expensive as</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>may</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr">
-        <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>I'd bought</t>
-        </is>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>have got</t>
-        </is>
-      </c>
-      <c r="AV30" t="inlineStr">
-        <is>
-          <t>I realize</t>
+          <t>did I realize</t>
         </is>
       </c>
     </row>
@@ -6966,152 +4734,77 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>More staff</t>
+          <t>More staff (1) _________ if sales increase.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>She</t>
+          <t>She (1) _________ his keys.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>If he hadn't cheated, he</t>
+          <t>If he hadn't cheated, he (1) _________ to pass.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>The team</t>
+          <t>The team (1) _________ very hard.</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (1) _________ down than the phone rang.</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>I don't think I can ever</t>
+          <t>I don't think I can ever (1) _________ this cold weather.</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>if sales increase.</t>
+          <t>will be hired</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>his keys.</t>
+          <t>reminded him to take</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>to pass.</t>
+          <t>would not have been able</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>very hard.</t>
+          <t>must have practiced</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>down than the phone rang.</t>
+          <t>sooner had I sat</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>this cold weather.</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>reminded</t>
+          <t>become accustomed to</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>would</t>
+          <t>wouldn't have been able</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>sooner</t>
+          <t>must have practised</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>become</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>be hired</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>him to take</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>not have been able</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>have practiced</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>had I sat</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>accustomed to</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>wouldn't</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>get</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr">
-        <is>
-          <t>have been able</t>
-        </is>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>have practised</t>
-        </is>
-      </c>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>accustomed to</t>
+          <t>get accustomed to</t>
         </is>
       </c>
     </row>
@@ -7183,152 +4876,77 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>The building</t>
+          <t>The building (1) _________ abandoned over fifty years ago.</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>The manager</t>
+          <t>The manager (1) _________ back to me sooner.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>The match</t>
+          <t>The match (1) _________ the heavy rain.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>The car</t>
+          <t>The car (1) _________ on its own.</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Hardly</t>
+          <t>Hardly (1) _________ at the office when the alarm went off.</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>It is a long time</t>
+          <t>It is a long time (1) _________ such a good movie.</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>abandoned over fifty years ago.</t>
+          <t>is thought to have been</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>back to me sooner.</t>
+          <t>apologised for not getting</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>the heavy rain.</t>
+          <t>would have gone ahead but for</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>on its own.</t>
+          <t>can't have just disappeared</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>at the office when the alarm went off.</t>
+          <t>had he arrived</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>such a good movie.</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>is</t>
+          <t>since I have seen</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>apologised</t>
+          <t>apologized for not getting</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>had</t>
+          <t>would not have been cancelled but for</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>since</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>thought to have been</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr">
-        <is>
-          <t>for not getting</t>
-        </is>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>have gone ahead but for</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>have just disappeared</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>he arrived</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>I have seen</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>apologized</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>would</t>
-        </is>
-      </c>
-      <c r="AQ32" t="inlineStr">
-        <is>
-          <t>since</t>
-        </is>
-      </c>
-      <c r="AS32" t="inlineStr">
-        <is>
-          <t>for not getting</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr">
-        <is>
-          <t>not have been cancelled but for</t>
-        </is>
-      </c>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>I last saw</t>
+          <t>since I last saw</t>
         </is>
       </c>
     </row>
@@ -7400,152 +5018,77 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>The city council plans</t>
+          <t>The city council plans (1) _________ next year.</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>David (1) _________ with the project.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>I wouldn't have made a huge mistake</t>
+          <t>I wouldn't have made a huge mistake (1) _________ to her.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ by the results.</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Under (1) _________ reveal your password to anyone.</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>It is</t>
+          <t>It is (1) _________ to go swimming today.</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>next year.</t>
+          <t>to have the old library renovated</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>with the project.</t>
+          <t>offered to help me</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>to her.</t>
+          <t>if I had listened</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>by the results.</t>
+          <t>must have been very disappointed</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>reveal your password to anyone.</t>
+          <t>no circumstances should you</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>to go swimming today.</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>to</t>
+          <t>not warm enough</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>offered</t>
+          <t>offered to give me a hand</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>if</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>if I'd listened</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>have the old library renovated</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr">
-        <is>
-          <t>to help me</t>
-        </is>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>I had listened</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>have been very disappointed</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>circumstances should you</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>warm enough</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>offered</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>if</t>
-        </is>
-      </c>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>n't</t>
-        </is>
-      </c>
-      <c r="AS33" t="inlineStr">
-        <is>
-          <t>to give me a hand</t>
-        </is>
-      </c>
-      <c r="AT33" t="inlineStr">
-        <is>
-          <t>I'd listened</t>
-        </is>
-      </c>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>warm enough</t>
+          <t>n't warm enough</t>
         </is>
       </c>
     </row>
@@ -7617,152 +5160,77 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>The painting</t>
+          <t>The painting (1) _________ worth millions.</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>The scientist</t>
+          <t>The scientist (1) _________ his idea.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>If it</t>
+          <t>If it (1) _________ your encouragement, I wouldn't have passed.</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ the invitation in time.</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Only after getting home</t>
+          <t>Only after getting home (1) _________ my phone was missing.</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ them, though they are not identical.</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>worth millions.</t>
+          <t>is believed to be</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>his idea.</t>
+          <t>accused his colleague of stealing</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>your encouragement, I wouldn't have passed.</t>
+          <t>had not been for</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>the invitation in time.</t>
+          <t>might not have received</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>my phone was missing.</t>
+          <t>did I realize (that)</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>them, though they are not identical.</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>accused</t>
+          <t>very little difference between</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>might</t>
+          <t>hadn't been for</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>did</t>
+          <t>did I realise (that)</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>very</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>believed to be</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>his colleague of stealing</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>not been for</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>not have received</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>I realize (that)</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>little difference between</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>hadn't</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AQ34" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr">
-        <is>
-          <t>been for</t>
-        </is>
-      </c>
-      <c r="AV34" t="inlineStr">
-        <is>
-          <t>I realise (that)</t>
-        </is>
-      </c>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>much difference between</t>
+          <t>not much difference between</t>
         </is>
       </c>
     </row>
@@ -7834,152 +5302,77 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>The house</t>
+          <t>The house (1) _________ by a famous architect.</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>My roommate</t>
+          <t>My roommate (1) _________ with the chores.</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>If it</t>
+          <t>If it (1) _________ your hint, I wouldn't have solved the problem.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ us because it was so dark.</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Hardly</t>
+          <t>Hardly (1) _________ the picnic when it began to pour with rain.</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Writing English is</t>
+          <t>Writing English is (1) _________ speaking it.</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>by a famous architect.</t>
+          <t>is thought to have been built</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>with the chores.</t>
+          <t>promised to help me</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>your hint, I wouldn't have solved the problem.</t>
+          <t>had not been for</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>us because it was so dark.</t>
+          <t>can't have seen</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>the picnic when it began to pour with rain.</t>
+          <t>had we started</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>speaking it.</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>is</t>
+          <t>not nearly as easy as</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>promised</t>
+          <t>promised to give me a hand</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>had</t>
+          <t>hadn't been for</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>thought to have been built</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>to help me</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>not been for</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>have seen</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>we started</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>nearly as easy as</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>promised</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>hadn't</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>to give me a hand</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr">
-        <is>
-          <t>been for</t>
-        </is>
-      </c>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>quite as easy as</t>
+          <t>not quite as easy as</t>
         </is>
       </c>
     </row>
@@ -8051,152 +5444,77 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ this afternoon.</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>The driver</t>
+          <t>The driver (1) _________ so late.</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ that car when I had the chance.</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ by the heavy traffic.</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Never (1) _________ such a beautiful view.</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>I am</t>
+          <t>I am (1) _________ the cold weather here.</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>this afternoon.</t>
+          <t>am having my teeth checked</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>so late.</t>
+          <t>apologised for being</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>that car when I had the chance.</t>
+          <t>wish I had bought</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>by the heavy traffic.</t>
+          <t>might have been delayed</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>such a beautiful view.</t>
+          <t>before had I seen</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>the cold weather here.</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>am</t>
+          <t>not accustomed to</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>apologised</t>
+          <t>apologized for being</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>before</t>
+          <t>wish I'd bought</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>having my teeth checked</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>for being</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>I had bought</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>have been delayed</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>had I seen</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>accustomed to</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>apologized</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>for being</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr">
-        <is>
-          <t>I'd bought</t>
-        </is>
-      </c>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>yet accustomed to</t>
+          <t>not yet accustomed to</t>
         </is>
       </c>
     </row>
@@ -8268,142 +5586,72 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>The results</t>
+          <t>The results (1) _________ at the end of the week.</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>The doctor</t>
+          <t>The doctor (1) _________ more exercise.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>You won't get there on time</t>
+          <t>You won't get there on time (1) _________ a taxi.</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ very tired after the long journey.</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Only when I saw the results</t>
+          <t>Only when I saw the results (1) _________ my mistake.</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ that we decided to stay indoors.</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>at the end of the week.</t>
+          <t>will be announced</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>more exercise.</t>
+          <t>advised me to take</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>a taxi.</t>
+          <t>unless you take</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>very tired after the long journey.</t>
+          <t>must have been</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>my mistake.</t>
+          <t>did I realize</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>that we decided to stay indoors.</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>advised</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>unless</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>must</t>
+          <t>was such a hot day</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>did</t>
+          <t>did I realise</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>be announced</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>me to take</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>you take</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>I realize</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>such a hot day</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AV37" t="inlineStr">
-        <is>
-          <t>I realise</t>
-        </is>
-      </c>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>such hot weather</t>
+          <t>was such hot weather</t>
         </is>
       </c>
     </row>
@@ -8475,152 +5723,77 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ the company is facing serious financial difficulties.</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>My brother</t>
+          <t>My brother (1) _________ to the airport.</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>If I had gone to the party, I</t>
+          <t>If I had gone to the party, I (1) _________ her.</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>You</t>
+          <t>You (1) _________ surprised when you won.</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>At no</t>
+          <t>At no (1) _________ been so happy.</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Learning Chinese is</t>
+          <t>Learning Chinese is (1) _________ as I expected.</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>the company is facing serious financial difficulties.</t>
+          <t>is widely believed that</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>to the airport.</t>
+          <t>offered to drive me</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>her.</t>
+          <t>would have met</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>surprised when you won.</t>
+          <t>must have been very</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>been so happy.</t>
+          <t>time had he ever</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>as I expected.</t>
+          <t>not nearly as easy</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>is generally believed that</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>offered</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>would</t>
+          <t>offered to take me</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>widely believed that</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>to drive me</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>have met</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>have been very</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>had he ever</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>nearly as easy</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>offered</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>generally believed that</t>
-        </is>
-      </c>
-      <c r="AS38" t="inlineStr">
-        <is>
-          <t>to take me</t>
-        </is>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>have been quite</t>
+          <t>must have been quite</t>
         </is>
       </c>
     </row>
@@ -8692,132 +5865,67 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (1) _________ at the moment.</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>My mother</t>
+          <t>My mother (1) _________ the door.</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ that house when I had the chance.</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ about the meeting.</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ she started speaking that I realized who she was.</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>I am</t>
+          <t>I am (1) _________ up early in the morning.</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>at the moment.</t>
+          <t>are having our living room decorated</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>the door.</t>
+          <t>reminded me to lock</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>that house when I had the chance.</t>
+          <t>wish I had bought</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>about the meeting.</t>
+          <t>might have forgotten</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>she started speaking that I realized who she was.</t>
+          <t>was only when</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>up early in the morning.</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>are</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>reminded</t>
+          <t>not used to getting</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>having our living room decorated</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>me to lock</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>I had bought</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>have forgotten</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>only when</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>used to getting</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr">
-        <is>
-          <t>I'd bought</t>
+          <t>wish I'd bought</t>
         </is>
       </c>
     </row>
@@ -8889,152 +5997,77 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>The old factory is</t>
+          <t>The old factory is (1) _________ next month.</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Thomas (1) _________ late.</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>I would not have passed the exam</t>
+          <t>I would not have passed the exam (1) _________ help.</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>The flooding</t>
+          <t>The flooding (1) _________ by the heavy rain.</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (1) _________ onto the court than it started to rain.</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ to convince him to change his mind.</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>next month.</t>
+          <t>going to be pulled down</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>late.</t>
+          <t>apologised for being</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>help.</t>
+          <t>but for his</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>by the heavy rain.</t>
+          <t>must have been caused</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>onto the court than it started to rain.</t>
+          <t>sooner had the players gone</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>to convince him to change his mind.</t>
+          <t>no point (in) trying</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>going to</t>
+          <t>due to be pulled down</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>apologised</t>
+          <t>apologized for being</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>but</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>sooner</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>be pulled down</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr">
-        <is>
-          <t>for being</t>
-        </is>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>for his</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>have been caused</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>had the players gone</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>point (in) trying</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>due to</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>apologized</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>but</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>be pulled down</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>for being</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr">
-        <is>
-          <t>for the help he gave</t>
+          <t>but for the help he gave</t>
         </is>
       </c>
     </row>
@@ -9106,132 +6139,67 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>The manuscript</t>
+          <t>The manuscript (1) _________ written in the 14th century.</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>My uncle</t>
+          <t>My uncle (1) _________ me to the airport.</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>I wouldn't have been late for work</t>
+          <t>I wouldn't have been late for work (1) _________ the road was closed.</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ the 'No Parking' sign.</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>No sooner</t>
+          <t>No sooner (1) _________ than the fire alarm went off.</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>There</t>
+          <t>There (1) _________ trying to fix that old computer.</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>written in the 14th century.</t>
+          <t>is believed to have been</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>me to the airport.</t>
+          <t>insisted on driving</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>the road was closed.</t>
+          <t>if I had known (that)</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>the 'No Parking' sign.</t>
+          <t>can't have seen</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>than the fire alarm went off.</t>
+          <t>had the meeting started</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>trying to fix that old computer.</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>insisted</t>
+          <t>is no point (in)</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>if</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>believed to have been</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>on driving</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>I had known (that)</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>have seen</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>the meeting started</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>no point (in)</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>if</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr">
-        <is>
-          <t>I'd known (that)</t>
+          <t>if I'd known (that)</t>
         </is>
       </c>
     </row>
@@ -9303,142 +6271,72 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (1) _________ as we speak.</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>The doctor</t>
+          <t>The doctor (1) _________ up smoking.</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ that job offer in Paris.</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ the last bus.</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Only when I checked the figures again</t>
+          <t>Only when I checked the figures again (1) _________ my mistake.</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ that everyone passed.</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>as we speak.</t>
+          <t>are having the leak repaired</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>up smoking.</t>
+          <t>advised him to give</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>that job offer in Paris.</t>
+          <t>wish I had taken</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>the last bus.</t>
+          <t>might have missed</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>my mistake.</t>
+          <t>did I realize</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>that everyone passed.</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>are</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>advised</t>
+          <t>was such an easy test</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>might</t>
+          <t>wish I'd taken</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>having the leak repaired</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr">
-        <is>
-          <t>him to give</t>
-        </is>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>I had taken</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>have missed</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>I realize</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>such an easy test</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr">
-        <is>
-          <t>I'd taken</t>
-        </is>
-      </c>
-      <c r="AV42" t="inlineStr">
-        <is>
-          <t>I realise</t>
+          <t>did I realise</t>
         </is>
       </c>
     </row>
@@ -9510,142 +6408,72 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>The winner</t>
+          <t>The winner (1) _________ later today.</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>The boy</t>
+          <t>The boy (1) _________ the window.</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>The project would have failed</t>
+          <t>The project would have failed (1) _________ your hard work.</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ with his results.</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Never before</t>
+          <t>Never before (1) _________ such a spectacular performance.</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ his logic.</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>later today.</t>
+          <t>is going to be announced</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>the window.</t>
+          <t>denied breaking</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>your hard work.</t>
+          <t>but for</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>with his results.</t>
+          <t>must have been happy</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>such a spectacular performance.</t>
+          <t>have I seen</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>his logic.</t>
+          <t>difficulty (in) understanding</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>is</t>
+          <t>will be announced</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>but</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>have</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>going to be announced</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr">
-        <is>
-          <t>breaking</t>
-        </is>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>have been happy</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>I seen</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>(in) understanding</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>be announced</t>
-        </is>
-      </c>
-      <c r="AS43" t="inlineStr">
-        <is>
-          <t>having broken</t>
+          <t>denied having broken</t>
         </is>
       </c>
     </row>
@@ -9717,142 +6545,72 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>The thief</t>
+          <t>The thief (1) _________ through the ventilation shaft.</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>The boy</t>
+          <t>The boy (1) _________ the broken window.</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>If</t>
+          <t>If (1) _________ the hole, I wouldn't have tripped and fallen.</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ a shock to hear the news.</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>The locked door</t>
+          <t>The locked door (1) _________ getting in.</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ I last went to the cinema.</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>through the ventilation shaft.</t>
+          <t>is thought to have entered</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>the broken window.</t>
+          <t>offered to pay for</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>the hole, I wouldn't have tripped and fallen.</t>
+          <t>I had seen</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>a shock to hear the news.</t>
+          <t>must have been</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>getting in.</t>
+          <t>prevented me from</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>I last went to the cinema.</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>offered</t>
+          <t>has been ages since</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>prevented</t>
+          <t>I had noticed</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>has</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>thought to have entered</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>to pay for</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>had seen</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>me from</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>been ages since</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="AQ44" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr">
-        <is>
-          <t>had noticed</t>
-        </is>
-      </c>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>ages since</t>
+          <t>is ages since</t>
         </is>
       </c>
     </row>
@@ -9924,152 +6682,77 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>We</t>
+          <t>We (1) _________ by the mechanic right now.</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>My friend</t>
+          <t>My friend (1) _________ a sport.</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ the truth.</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ the message.</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ the lights went out that I realized it was so late.</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>There</t>
+          <t>There (1) _________ for us to find a table.</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>by the mechanic right now.</t>
+          <t>are having our car serviced</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>a sport.</t>
+          <t>advised me to take up</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>the truth.</t>
+          <t>wish I had told you</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>the message.</t>
+          <t>might not have received</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>the lights went out that I realized it was so late.</t>
+          <t>was only when</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>for us to find a table.</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>are</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>advised</t>
+          <t>was not enough room</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>wish</t>
+          <t>wish I'd told you</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>was</t>
+          <t>might not have got</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>having our car serviced</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>me to take up</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>I had told you</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>not have received</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>only when</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>not enough room</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>might</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>were</t>
-        </is>
-      </c>
-      <c r="AT45" t="inlineStr">
-        <is>
-          <t>I'd told you</t>
-        </is>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>not have got</t>
-        </is>
-      </c>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>not enough tables</t>
+          <t>were not enough tables</t>
         </is>
       </c>
     </row>
@@ -10141,132 +6824,67 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>The results</t>
+          <t>The results (1) _________ at the end of the day.</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ late.</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>I wouldn't have passed the test</t>
+          <t>I wouldn't have passed the test (1) _________ all night.</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ with his new job.</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Never before</t>
+          <t>Never before (1) _________ such a beautiful sunrise.</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ to open that door.</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>at the end of the day.</t>
+          <t>will be announced</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>late.</t>
+          <t>promised his mother (that) he wouldn't</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>all night.</t>
+          <t>unless I had studied</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>with his new job.</t>
+          <t>must have been happy</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>such a beautiful sunrise.</t>
+          <t>had he seen</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>to open that door.</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>will</t>
+          <t>no point (in) trying</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>promised</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>unless</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>be announced</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>his mother (that) he wouldn't</t>
-        </is>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>I had studied</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>have been happy</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>he seen</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>point (in) trying</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>promised</t>
-        </is>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>not to be</t>
+          <t>promised not to be</t>
         </is>
       </c>
     </row>
@@ -10338,132 +6956,67 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>The criminal</t>
+          <t>The criminal (1) _________ somewhere in the city.</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>My aunt</t>
+          <t>My aunt (1) _________ to my graduation.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>I wouldn't have got lost if I</t>
+          <t>I wouldn't have got lost if I (1) _________ the map.</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Mark (1) _________ responsible for the error.</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Scarcely</t>
+          <t>Scarcely (1) _________ when the power failed.</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ a new phone if yours still works.</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>somewhere in the city.</t>
+          <t>is thought to be hiding</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>to my graduation.</t>
+          <t>apologised for not coming</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>the map.</t>
+          <t>had taken</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>responsible for the error.</t>
+          <t>can't have been</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>when the power failed.</t>
+          <t>had the concert started</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>a new phone if yours still works.</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>is</t>
+          <t>no point (in) buying</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>apologised</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>thought to be hiding</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr">
-        <is>
-          <t>for not coming</t>
-        </is>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>taken</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>the concert started</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>point (in) buying</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>apologized</t>
-        </is>
-      </c>
-      <c r="AS47" t="inlineStr">
-        <is>
-          <t>for not coming</t>
+          <t>apologized for not coming</t>
         </is>
       </c>
     </row>
@@ -10535,142 +7088,72 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>The company is</t>
+          <t>The company is (1) _________ by a professional.</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>The guide</t>
+          <t>The guide (1) _________ too near the edge.</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ the piano when I was a child.</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>They</t>
+          <t>They (1) _________ the email until this morning.</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Only after sending the letter</t>
+          <t>Only after sending the letter (1) _________ my mistake.</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ that I couldn't finish it.</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>by a professional.</t>
+          <t>having the document translated</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>too near the edge.</t>
+          <t>warned the tourists not to go</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>the piano when I was a child.</t>
+          <t>wish I had learned to play</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>the email until this morning.</t>
+          <t>might not have seen</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>my mistake.</t>
+          <t>did I realize</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>that I couldn't finish it.</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>having</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>warned</t>
+          <t>was such a difficult exercise</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>might</t>
+          <t>wish I'd learned to play</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>the document translated</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr">
-        <is>
-          <t>the tourists not to go</t>
-        </is>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>I had learned to play</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>not have seen</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>I realize</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>such a difficult exercise</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AP48" t="inlineStr">
-        <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AT48" t="inlineStr">
-        <is>
-          <t>I'd learned to play</t>
-        </is>
-      </c>
-      <c r="AV48" t="inlineStr">
-        <is>
-          <t>I realise</t>
+          <t>did I realise</t>
         </is>
       </c>
     </row>
@@ -10742,132 +7225,67 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>The old cinema</t>
+          <t>The old cinema (1) _________ next year.</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Paul (1) _________ for the coffee.</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>If I</t>
+          <t>If I (1) _________ money, I would have bought the tickets.</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ happy to hear the news.</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>It</t>
+          <t>It (1) _________ he spoke that I knew who he was.</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>I have</t>
+          <t>I have (1) _________ the noise in the city.</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>next year.</t>
+          <t>will be renovated</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>for the coffee.</t>
+          <t>insisted on paying</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>money, I would have bought the tickets.</t>
+          <t>had had enough</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>happy to hear the news.</t>
+          <t>must have been very</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>he spoke that I knew who he was.</t>
+          <t>was only when</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>the noise in the city.</t>
+          <t>difficulty (in) getting used to</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>will</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>insisted</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>had</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>must</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>was</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>difficulty</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>be renovated</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>on paying</t>
-        </is>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>had enough</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>have been very</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>only when</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>(in) getting used to</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>is</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>going to be renovated</t>
+          <t>is going to be renovated</t>
         </is>
       </c>
     </row>
@@ -10939,132 +7357,67 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>The missing climber</t>
+          <t>The missing climber (1) _________ found safe.</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Sarah apologised</t>
+          <t>Sarah apologised (1) _________ to post my letter.</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Had it</t>
+          <t>Had it (1) _________ help, I wouldn't have finished the project.</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>He (1) _________ at home when the accident happened.</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (1) _________ at the station than the train left.</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>There is</t>
+          <t>There is (1) _________ to convince him.</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>found safe.</t>
+          <t>is reported to have been</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>to post my letter.</t>
+          <t>for forgetting</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>help, I wouldn't have finished the project.</t>
+          <t>not been for your</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>at home when the accident happened.</t>
+          <t>can't have been</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>at the station than the train left.</t>
+          <t>sooner had I arrived</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>to convince him.</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>is</t>
+          <t>no point (in) trying</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>not</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>can't</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>sooner</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>reported to have been</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr">
-        <is>
-          <t>forgetting</t>
-        </is>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>been for your</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>have been</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>had I arrived</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>point (in) trying</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>for</t>
-        </is>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>having forgotten</t>
+          <t>for having forgotten</t>
         </is>
       </c>
     </row>
@@ -11136,152 +7489,77 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>We are going</t>
+          <t>We are going (1) _________ by a local builder next week.</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>The doctor</t>
+          <t>The doctor (1) _________ eating too much junk food.</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>I (1) _________ you at the party.</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>The cat</t>
+          <t>The cat (1) _________ in the garage.</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Only after getting home</t>
+          <t>Only after getting home (1) _________ my phone was missing.</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>It was</t>
+          <t>It was (1) _________ that I didn't want it to end.</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>by a local builder next week.</t>
+          <t>to have our roof repaired</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>eating too much junk food.</t>
+          <t>advised me to avoid</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>you at the party.</t>
+          <t>wish I had seen</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>in the garage.</t>
+          <t>might have been trapped</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>my phone was missing.</t>
+          <t>did I realize</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>that I didn't want it to end.</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>to</t>
+          <t>such an exciting match</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>advised</t>
+          <t>advised against</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>might</t>
+          <t>wish I'd seen</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>such</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>have our roof repaired</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr">
-        <is>
-          <t>me to avoid</t>
-        </is>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>I had seen</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>have been trapped</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>I realize</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>an exciting match</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>advised</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>wish</t>
-        </is>
-      </c>
-      <c r="AP51" t="inlineStr">
-        <is>
-          <t>did</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>against</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr">
-        <is>
-          <t>I'd seen</t>
-        </is>
-      </c>
-      <c r="AV51" t="inlineStr">
-        <is>
-          <t>I realise</t>
+          <t>did I realise</t>
         </is>
       </c>
     </row>
